--- a/data/trans_dic/P16A02-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P16A02-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para el dolor/bajar la fiebre en las dos últimas semanas</t>
+          <t>Población que ha consumido medicinas para el dolor/bajar la fiebre en las dos últimas semanas (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,6; 10,77</t>
+          <t>5,53; 10,09</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,9; 15,27</t>
+          <t>8,98; 15,42</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,9; 15,28</t>
+          <t>8,92; 15,69</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,7; 18,37</t>
+          <t>7,16; 19,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>14,28; 21,17</t>
+          <t>14,3; 21,13</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,73; 26,46</t>
+          <t>18,8; 26,43</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,99; 21,43</t>
+          <t>13,68; 21,27</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13,99; 26,22</t>
+          <t>14,5; 26,71</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,38; 14,49</t>
+          <t>10,14; 14,57</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14,45; 19,75</t>
+          <t>14,51; 19,83</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12,17; 17,33</t>
+          <t>12,19; 17,16</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,51; 20,11</t>
+          <t>11,71; 19,96</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,91; 11,07</t>
+          <t>6,79; 11,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11,83; 17,47</t>
+          <t>12,15; 17,66</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13,6; 19,76</t>
+          <t>13,78; 20,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14,71; 24,69</t>
+          <t>14,17; 24,49</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,29; 17,93</t>
+          <t>12,15; 17,91</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,85; 27,89</t>
+          <t>20,83; 28,17</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,9; 26,68</t>
+          <t>19,93; 27,08</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,52; 23,97</t>
+          <t>11,56; 23,93</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,73; 13,21</t>
+          <t>9,8; 13,25</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17,1; 21,71</t>
+          <t>17,22; 21,64</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17,83; 22,44</t>
+          <t>17,86; 22,57</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>14,5; 22,3</t>
+          <t>14,73; 22,59</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11,01; 16,34</t>
+          <t>10,66; 16,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,15; 17,89</t>
+          <t>12,01; 17,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14,58; 20,27</t>
+          <t>14,6; 20,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15,34; 22,59</t>
+          <t>15,25; 22,44</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17,51; 23,96</t>
+          <t>17,3; 23,63</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>27,27; 34,42</t>
+          <t>27,13; 34,22</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,73; 27,26</t>
+          <t>20,66; 27,18</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>27,66; 34,24</t>
+          <t>27,34; 34,35</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>15,26; 19,27</t>
+          <t>15,04; 19,2</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>20,6; 25,27</t>
+          <t>20,66; 25,32</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18,24; 22,71</t>
+          <t>18,39; 23,0</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>22,48; 27,54</t>
+          <t>22,51; 27,27</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12,28; 18,5</t>
+          <t>12,03; 17,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,49; 19,54</t>
+          <t>13,62; 19,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,5; 23,03</t>
+          <t>16,43; 23,25</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,86; 26,38</t>
+          <t>8,06; 26,79</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>20,15; 27,41</t>
+          <t>20,02; 27,52</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,16; 35,84</t>
+          <t>28,1; 36,17</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,61; 33,55</t>
+          <t>25,2; 32,77</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>30,94; 40,45</t>
+          <t>30,45; 40,12</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16,78; 21,94</t>
+          <t>17,1; 22,2</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21,82; 26,74</t>
+          <t>21,7; 26,82</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21,97; 26,95</t>
+          <t>21,9; 26,75</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>16,1; 32,38</t>
+          <t>16,75; 32,38</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>18,03; 26,57</t>
+          <t>18,07; 26,29</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>18,0; 26,39</t>
+          <t>18,15; 26,45</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18,95; 27,27</t>
+          <t>18,97; 26,48</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26,48; 33,64</t>
+          <t>26,47; 33,8</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>24,58; 34,01</t>
+          <t>24,85; 33,72</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,68; 40,56</t>
+          <t>31,49; 40,74</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,1; 44,46</t>
+          <t>35,0; 44,1</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>41,47; 47,55</t>
+          <t>41,44; 47,55</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>22,48; 28,67</t>
+          <t>22,54; 28,45</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26,01; 32,35</t>
+          <t>25,97; 32,33</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27,94; 34,45</t>
+          <t>28,28; 34,55</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>34,94; 39,68</t>
+          <t>34,74; 39,75</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12,6; 21,21</t>
+          <t>12,75; 21,37</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>21,42; 32,74</t>
+          <t>21,35; 32,35</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13,98; 22,39</t>
+          <t>14,16; 22,47</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>23,5; 30,84</t>
+          <t>23,88; 31,53</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>27,92; 37,32</t>
+          <t>27,68; 37,5</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>40,19; 51,63</t>
+          <t>40,41; 50,56</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>38,48; 48,67</t>
+          <t>38,45; 48,4</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>51,76; 86,34</t>
+          <t>51,34; 85,33</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>22,12; 28,34</t>
+          <t>21,96; 28,43</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>33,21; 40,66</t>
+          <t>33,23; 40,9</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>27,77; 34,98</t>
+          <t>27,79; 34,8</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>39,7; 74,44</t>
+          <t>39,91; 74,87</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>20,91; 32,66</t>
+          <t>20,48; 32,07</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>25,5; 38,29</t>
+          <t>25,89; 38,66</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>27,15; 38,01</t>
+          <t>26,97; 37,3</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>35,17; 44,56</t>
+          <t>35,88; 44,92</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>35,89; 47,23</t>
+          <t>36,25; 47,49</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>47,78; 58,29</t>
+          <t>48,24; 58,22</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>43,75; 54,85</t>
+          <t>43,86; 54,94</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>63,7; 70,24</t>
+          <t>63,79; 70,49</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>31,54; 40,32</t>
+          <t>31,71; 40,15</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>40,77; 48,9</t>
+          <t>40,41; 48,52</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>38,36; 46,72</t>
+          <t>37,7; 46,52</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>53,2; 58,92</t>
+          <t>53,63; 59,16</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>12,8; 15,25</t>
+          <t>12,82; 15,08</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>16,55; 19,24</t>
+          <t>16,51; 19,39</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17,67; 20,21</t>
+          <t>17,57; 20,19</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17,4; 24,74</t>
+          <t>17,53; 24,92</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>22,52; 25,42</t>
+          <t>22,43; 25,37</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>31,8; 35,15</t>
+          <t>31,96; 35,14</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,45; 32,61</t>
+          <t>29,51; 32,79</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>37,91; 53,16</t>
+          <t>37,63; 51,57</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>18,03; 19,95</t>
+          <t>17,99; 19,95</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>24,79; 26,98</t>
+          <t>24,81; 27,02</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24,02; 26,25</t>
+          <t>24,12; 26,36</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>29,14; 39,03</t>
+          <t>29,35; 38,79</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para el dolor/bajar la fiebre en las dos últimas semanas</t>
+          <t>Población que ha consumido medicinas para el dolor/bajar la fiebre en las dos últimas semanas (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>27683; 53197</t>
+          <t>27311; 49872</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>40329; 69179</t>
+          <t>40711; 69875</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>37317; 64114</t>
+          <t>37420; 65799</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26784; 73481</t>
+          <t>28627; 76824</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>66735; 98962</t>
+          <t>66838; 98789</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>80414; 113612</t>
+          <t>80700; 113484</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>55358; 84793</t>
+          <t>54153; 84194</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>43814; 82113</t>
+          <t>45423; 83656</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>99829; 139291</t>
+          <t>97510; 140115</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>127552; 174286</t>
+          <t>128003; 174945</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>99234; 141251</t>
+          <t>99364; 139874</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>82105; 143410</t>
+          <t>83539; 142330</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>50805; 81388</t>
+          <t>49936; 81865</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>81206; 119861</t>
+          <t>83360; 121204</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>80315; 116711</t>
+          <t>81365; 118764</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>62287; 104568</t>
+          <t>60002; 103746</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>76886; 112128</t>
+          <t>76014; 112008</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>127024; 169923</t>
+          <t>126914; 171622</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>112137; 150376</t>
+          <t>112335; 152592</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>58940; 122604</t>
+          <t>59132; 122400</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>132464; 179767</t>
+          <t>133337; 180387</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>221565; 281206</t>
+          <t>223018; 280323</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>205769; 258991</t>
+          <t>206058; 260412</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>135590; 208501</t>
+          <t>137708; 211203</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>70174; 104176</t>
+          <t>67983; 102953</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>82617; 121635</t>
+          <t>81668; 120087</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>97575; 135648</t>
+          <t>97656; 136173</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>82264; 121180</t>
+          <t>81778; 120358</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>120785; 165259</t>
+          <t>119358; 163012</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>193248; 243902</t>
+          <t>192276; 242482</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>137080; 180297</t>
+          <t>136646; 179736</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>150026; 185725</t>
+          <t>148316; 186327</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>202527; 255735</t>
+          <t>199674; 254873</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>286107; 350854</t>
+          <t>286968; 351615</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>242736; 302186</t>
+          <t>244678; 306068</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>242517; 297122</t>
+          <t>242888; 294243</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>63736; 96037</t>
+          <t>62446; 93341</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>82942; 120095</t>
+          <t>83720; 120993</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>106614; 148798</t>
+          <t>106121; 150231</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>69818; 234218</t>
+          <t>71515; 237873</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>103888; 141360</t>
+          <t>103246; 141927</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>172936; 220111</t>
+          <t>172582; 222137</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>166228; 217782</t>
+          <t>163596; 212733</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>220578; 288361</t>
+          <t>217083; 286034</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>173606; 227048</t>
+          <t>176969; 229761</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>268054; 328582</t>
+          <t>266648; 329574</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>284553; 348988</t>
+          <t>283572; 346482</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>257758; 518345</t>
+          <t>268114; 518326</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>69724; 102752</t>
+          <t>69896; 101661</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>77121; 113043</t>
+          <t>77728; 113317</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>90548; 130350</t>
+          <t>90661; 126533</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>148593; 188776</t>
+          <t>148560; 189691</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>99302; 137388</t>
+          <t>100373; 136219</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>137394; 181606</t>
+          <t>141005; 182455</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>174380; 220896</t>
+          <t>173910; 219091</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>225941; 259087</t>
+          <t>225827; 259085</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>177720; 226727</t>
+          <t>178237; 224947</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>227855; 283474</t>
+          <t>227545; 283251</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>272318; 335833</t>
+          <t>275702; 336735</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>386485; 438940</t>
+          <t>384250; 439665</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>36865; 62047</t>
+          <t>37313; 62536</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>66366; 101423</t>
+          <t>66151; 100213</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>46753; 74848</t>
+          <t>47332; 75111</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>86530; 113533</t>
+          <t>87922; 116070</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>95747; 127994</t>
+          <t>94922; 128599</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>142280; 182784</t>
+          <t>143049; 178981</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>145375; 183840</t>
+          <t>145262; 182842</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>314878; 525280</t>
+          <t>312339; 519100</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>140575; 180124</t>
+          <t>139547; 180681</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>220411; 269923</t>
+          <t>220554; 271456</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>197737; 249056</t>
+          <t>197898; 247807</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>387720; 726977</t>
+          <t>389747; 731105</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>43878; 68550</t>
+          <t>42989; 67318</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>63515; 95346</t>
+          <t>64468; 96277</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>69773; 97681</t>
+          <t>69319; 95849</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>99438; 125997</t>
+          <t>101458; 127022</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>119824; 157708</t>
+          <t>121052; 158560</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>185340; 226140</t>
+          <t>187123; 225851</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>175077; 219497</t>
+          <t>175521; 219858</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>270896; 298727</t>
+          <t>271291; 299781</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>171521; 219262</t>
+          <t>172445; 218349</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>259704; 311477</t>
+          <t>257373; 309074</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>252104; 307036</t>
+          <t>247740; 305717</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>376715; 417173</t>
+          <t>379705; 418874</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>419332; 499643</t>
+          <t>419788; 494030</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>566113; 658389</t>
+          <t>564915; 663418</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>599790; 685922</t>
+          <t>596489; 685443</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>602104; 855818</t>
+          <t>606557; 862316</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>760960; 859025</t>
+          <t>758119; 857376</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1129279; 1248204</t>
+          <t>1134909; 1247662</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1043727; 1156043</t>
+          <t>1045830; 1162104</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1387080; 1944977</t>
+          <t>1376601; 1886597</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1199751; 1327515</t>
+          <t>1197256; 1327501</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1728497; 1880953</t>
+          <t>1729485; 1884212</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1666980; 1821371</t>
+          <t>1673737; 1828832</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>2074461; 2778298</t>
+          <t>2089193; 2761143</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A02-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P16A02-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,91%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,53; 10,09</t>
+          <t>5,66; 10,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,98; 15,42</t>
+          <t>8,99; 15,42</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,92; 15,69</t>
+          <t>8,83; 15,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,16; 19,21</t>
+          <t>7,19; 17,4</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>14,3; 21,13</t>
+          <t>14,0; 20,62</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,8; 26,43</t>
+          <t>18,69; 26,63</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,68; 21,27</t>
+          <t>13,87; 20,87</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>14,5; 26,71</t>
+          <t>15,4; 27,12</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,14; 14,57</t>
+          <t>10,65; 14,74</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14,51; 19,83</t>
+          <t>14,54; 19,86</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12,19; 17,16</t>
+          <t>12,23; 17,22</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,71; 19,96</t>
+          <t>12,6; 20,35</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,7%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,79; 11,13</t>
+          <t>6,8; 10,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,15; 17,66</t>
+          <t>12,26; 17,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13,78; 20,11</t>
+          <t>13,79; 19,99</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14,17; 24,49</t>
+          <t>13,84; 23,86</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,15; 17,91</t>
+          <t>11,76; 17,8</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,83; 28,17</t>
+          <t>20,68; 28,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,93; 27,08</t>
+          <t>19,85; 26,85</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,56; 23,93</t>
+          <t>17,04; 24,48</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,8; 13,25</t>
+          <t>9,84; 13,38</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17,22; 21,64</t>
+          <t>17,18; 21,8</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17,86; 22,57</t>
+          <t>17,73; 22,4</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>14,73; 22,59</t>
+          <t>16,5; 23,11</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>24,22%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10,66; 16,15</t>
+          <t>10,95; 16,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,01; 17,66</t>
+          <t>12,15; 17,55</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14,6; 20,35</t>
+          <t>14,47; 20,42</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15,25; 22,44</t>
+          <t>14,87; 21,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17,3; 23,63</t>
+          <t>17,74; 23,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>27,13; 34,22</t>
+          <t>27,3; 34,59</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,66; 27,18</t>
+          <t>20,65; 27,23</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>27,34; 34,35</t>
+          <t>27,23; 33,75</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>15,04; 19,2</t>
+          <t>15,0; 19,28</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>20,66; 25,32</t>
+          <t>20,59; 25,26</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18,39; 23,0</t>
+          <t>18,5; 22,89</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>22,51; 27,27</t>
+          <t>22,03; 26,97</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>31,51%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12,03; 17,98</t>
+          <t>11,91; 18,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,62; 19,69</t>
+          <t>13,75; 19,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,43; 23,25</t>
+          <t>16,31; 22,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,06; 26,79</t>
+          <t>21,54; 28,67</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>20,02; 27,52</t>
+          <t>20,31; 27,71</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,1; 36,17</t>
+          <t>27,78; 36,12</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,2; 32,77</t>
+          <t>25,19; 32,98</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>30,45; 40,12</t>
+          <t>34,82; 40,38</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>17,1; 22,2</t>
+          <t>16,95; 21,79</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21,7; 26,82</t>
+          <t>21,73; 26,76</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21,9; 26,75</t>
+          <t>22,12; 26,9</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>16,75; 32,38</t>
+          <t>29,38; 33,9</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>44,43%</t>
+          <t>44,28%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>37,09%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>18,07; 26,29</t>
+          <t>18,16; 26,75</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>18,15; 26,45</t>
+          <t>18,43; 26,97</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18,97; 26,48</t>
+          <t>19,1; 26,7</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26,47; 33,8</t>
+          <t>26,54; 33,36</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>24,85; 33,72</t>
+          <t>24,12; 33,22</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,49; 40,74</t>
+          <t>31,38; 40,92</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,0; 44,1</t>
+          <t>34,94; 44,22</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>41,44; 47,55</t>
+          <t>41,2; 47,24</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>22,54; 28,45</t>
+          <t>22,48; 28,48</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25,97; 32,33</t>
+          <t>26,23; 32,41</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28,28; 34,55</t>
+          <t>28,37; 34,07</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>34,74; 39,75</t>
+          <t>34,79; 39,42</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>68,66%</t>
+          <t>52,66%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>53,15%</t>
+          <t>40,31%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12,75; 21,37</t>
+          <t>12,69; 21,43</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>21,35; 32,35</t>
+          <t>21,86; 32,1</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14,16; 22,47</t>
+          <t>13,77; 22,55</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>23,88; 31,53</t>
+          <t>23,71; 30,81</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>27,68; 37,5</t>
+          <t>28,17; 37,38</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>40,41; 50,56</t>
+          <t>40,24; 50,56</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>38,45; 48,4</t>
+          <t>37,63; 48,06</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>51,34; 85,33</t>
+          <t>49,31; 56,08</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>21,96; 28,43</t>
+          <t>21,86; 28,42</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>33,23; 40,9</t>
+          <t>33,27; 40,72</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>27,79; 34,8</t>
+          <t>27,78; 34,85</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>39,91; 74,87</t>
+          <t>37,83; 43,12</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>39,72%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>67,08%</t>
+          <t>66,61%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>56,32%</t>
+          <t>55,83%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>20,48; 32,07</t>
+          <t>20,49; 32,19</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>25,89; 38,66</t>
+          <t>25,61; 37,99</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>26,97; 37,3</t>
+          <t>26,71; 37,58</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>35,88; 44,92</t>
+          <t>34,97; 44,34</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>36,25; 47,49</t>
+          <t>36,15; 47,18</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>48,24; 58,22</t>
+          <t>47,98; 57,93</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>43,86; 54,94</t>
+          <t>43,58; 55,24</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>63,79; 70,49</t>
+          <t>63,28; 69,83</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>31,71; 40,15</t>
+          <t>31,61; 40,47</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>40,41; 48,52</t>
+          <t>40,48; 48,75</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>37,7; 46,52</t>
+          <t>38,77; 46,74</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>53,63; 59,16</t>
+          <t>53,17; 58,65</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>38,96%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>31,57%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>12,82; 15,08</t>
+          <t>12,79; 15,17</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>16,51; 19,39</t>
+          <t>16,42; 19,32</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17,57; 20,19</t>
+          <t>17,53; 20,27</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17,53; 24,92</t>
+          <t>22,26; 25,43</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>22,43; 25,37</t>
+          <t>22,27; 25,25</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>31,96; 35,14</t>
+          <t>31,8; 35,11</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,51; 32,79</t>
+          <t>29,64; 32,77</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>37,63; 51,57</t>
+          <t>37,54; 40,24</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>17,99; 19,95</t>
+          <t>17,95; 19,93</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>24,81; 27,02</t>
+          <t>24,74; 26,97</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24,12; 26,36</t>
+          <t>24,12; 26,16</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>29,35; 38,79</t>
+          <t>30,63; 32,62</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>46435</t>
+          <t>47676</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>62773</t>
+          <t>74848</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>109208</t>
+          <t>122523</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>27311; 49872</t>
+          <t>27961; 50782</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>40711; 69875</t>
+          <t>40713; 69855</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>37420; 65799</t>
+          <t>37056; 66310</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>28627; 76824</t>
+          <t>29319; 70972</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>66838; 98789</t>
+          <t>65442; 96404</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>80700; 113484</t>
+          <t>80237; 114321</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>54153; 84194</t>
+          <t>54872; 82595</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>45423; 83656</t>
+          <t>55830; 98326</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>97510; 140115</t>
+          <t>102440; 141754</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>128003; 174945</t>
+          <t>128304; 175233</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>99364; 139874</t>
+          <t>99676; 140359</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>83539; 142330</t>
+          <t>97059; 156748</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>80559</t>
+          <t>88636</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>97484</t>
+          <t>103976</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>178043</t>
+          <t>192612</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>49936; 81865</t>
+          <t>50030; 79488</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>83360; 121204</t>
+          <t>84129; 120822</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>81365; 118764</t>
+          <t>81441; 118036</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>60002; 103746</t>
+          <t>66012; 113786</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>76014; 112008</t>
+          <t>73583; 111324</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>126914; 171622</t>
+          <t>125971; 170608</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>112335; 152592</t>
+          <t>111840; 151306</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>59132; 122400</t>
+          <t>85373; 122651</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>133337; 180387</t>
+          <t>133892; 182093</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>223018; 280323</t>
+          <t>222545; 282390</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>206058; 260412</t>
+          <t>204662; 258552</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>137708; 211203</t>
+          <t>161367; 225968</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>101343</t>
+          <t>111685</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>166970</t>
+          <t>189333</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>268313</t>
+          <t>301019</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>67983; 102953</t>
+          <t>69824; 105944</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>81668; 120087</t>
+          <t>82598; 119378</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>97656; 136173</t>
+          <t>96806; 136599</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>81778; 120358</t>
+          <t>92332; 133959</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>119358; 163012</t>
+          <t>122393; 163612</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>192276; 242482</t>
+          <t>193483; 245083</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>136646; 179736</t>
+          <t>136597; 180126</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>148316; 186327</t>
+          <t>169434; 209993</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>199674; 254873</t>
+          <t>199050; 255951</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>286968; 351615</t>
+          <t>285895; 350845</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>244678; 306068</t>
+          <t>246180; 304488</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>242888; 294243</t>
+          <t>273781; 335286</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>163677</t>
+          <t>175859</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>262044</t>
+          <t>277043</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>425721</t>
+          <t>452902</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>62446; 93341</t>
+          <t>61852; 95558</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>83720; 120993</t>
+          <t>84500; 121172</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>106121; 150231</t>
+          <t>105362; 148233</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>71515; 237873</t>
+          <t>150941; 200856</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>103246; 141927</t>
+          <t>104712; 142865</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>172582; 222137</t>
+          <t>170583; 221791</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>163596; 212733</t>
+          <t>163519; 214073</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>217083; 286034</t>
+          <t>256590; 297527</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>176969; 229761</t>
+          <t>175381; 225503</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>266648; 329574</t>
+          <t>266979; 328846</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>283572; 346482</t>
+          <t>286509; 348452</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>268114; 518326</t>
+          <t>422403; 487329</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>170006</t>
+          <t>182384</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>242091</t>
+          <t>268976</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>412097</t>
+          <t>451360</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>69896; 101661</t>
+          <t>70220; 103427</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>77728; 113317</t>
+          <t>78962; 115528</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>90661; 126533</t>
+          <t>91295; 127611</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>148560; 189691</t>
+          <t>161709; 203282</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>100373; 136219</t>
+          <t>97429; 134192</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>141005; 182455</t>
+          <t>140522; 183255</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>173910; 219091</t>
+          <t>173607; 219683</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>225827; 259085</t>
+          <t>250285; 286974</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>178237; 224947</t>
+          <t>177774; 225222</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>227545; 283251</t>
+          <t>229831; 283932</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>275702; 336735</t>
+          <t>276510; 332145</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>384250; 439665</t>
+          <t>423383; 479657</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>101263</t>
+          <t>109883</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>417722</t>
+          <t>231270</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>518985</t>
+          <t>341154</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>37313; 62536</t>
+          <t>37116; 62693</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>66151; 100213</t>
+          <t>67707; 99453</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>47332; 75111</t>
+          <t>46021; 75407</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>87922; 116070</t>
+          <t>96519; 125437</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>94922; 128599</t>
+          <t>96605; 128190</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>143049; 178981</t>
+          <t>142457; 178979</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>145262; 182842</t>
+          <t>142157; 181554</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>312339; 519100</t>
+          <t>216551; 246272</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>139547; 180681</t>
+          <t>138899; 180612</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>220554; 271456</t>
+          <t>220815; 270264</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>197898; 247807</t>
+          <t>197844; 248157</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>389747; 731105</t>
+          <t>320120; 364926</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>113511</t>
+          <t>123203</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>285297</t>
+          <t>309062</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>398808</t>
+          <t>432266</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>42989; 67318</t>
+          <t>43004; 67569</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>64468; 96277</t>
+          <t>63776; 94607</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>69319; 95849</t>
+          <t>68632; 96574</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>101458; 127022</t>
+          <t>108490; 137537</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>121052; 158560</t>
+          <t>120701; 157521</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>187123; 225851</t>
+          <t>186114; 224748</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>175521; 219858</t>
+          <t>174394; 221051</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>271291; 299781</t>
+          <t>293625; 324008</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>172445; 218349</t>
+          <t>171900; 220046</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>257373; 309074</t>
+          <t>257864; 310511</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>247740; 305717</t>
+          <t>254790; 307182</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>379705; 418874</t>
+          <t>411675; 454072</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>776794</t>
+          <t>839327</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>1534383</t>
+          <t>1454508</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>2311177</t>
+          <t>2293836</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>419788; 494030</t>
+          <t>418796; 496828</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>564915; 663418</t>
+          <t>561679; 661042</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>596489; 685443</t>
+          <t>595150; 688038</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>606557; 862316</t>
+          <t>786469; 898424</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>758119; 857376</t>
+          <t>752583; 853098</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1134909; 1247662</t>
+          <t>1129220; 1246793</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1045830; 1162104</t>
+          <t>1050441; 1161428</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1376601; 1886597</t>
+          <t>1401329; 1502432</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1197256; 1327501</t>
+          <t>1194525; 1326086</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1729485; 1884212</t>
+          <t>1725197; 1880104</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1673737; 1828832</t>
+          <t>1673551; 1815264</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>2089193; 2761143</t>
+          <t>2225276; 2370307</t>
         </is>
       </c>
     </row>
